--- a/results_OV3heads_dlrsd_v0b_seghead_decoderlast2_4x4090.xlsx
+++ b/results_OV3heads_dlrsd_v0b_seghead_decoderlast2_4x4090.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,27 @@
         <v>70.66999816894531</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>iSAIDDataset</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>93.94999694824219</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.97000122070312</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
